--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="337">
   <si>
     <t>Result</t>
   </si>
@@ -802,6 +802,288 @@
   </si>
   <si>
     <t>Thu Jun 04 23:39:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 20:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:44:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:51:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:53:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 22:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:00:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:01:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:02:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:05:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:06:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:07:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:10:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:11:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:16:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:17:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:27:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:28:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:31:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:32:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:37:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:39:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:43:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:45:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:49:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 18 23:56:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:03:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:05:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:10:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:15:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:24:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:28:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:30:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:33:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 00:35:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 17:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:24:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:37:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 18:42:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 19:03:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 19:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 19 22:59:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:38:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:40:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:42:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:49:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:56:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:57:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 01:58:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:03:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:05:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:06:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:07:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:13:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:15:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:16:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:20:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:22:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:23:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:25:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:27:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:34:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:40:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:57:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 02:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:00:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:05:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:11:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:25:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:27:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 20 03:32:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 20:57:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 21:10:34 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED741D40-69F4-4234-A010-FAFEF4635982}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1188,11 +1470,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>230</v>
+      <c r="B2" t="s" s="0">
+        <v>311</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1234,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1AA3-AD23-49E0-84C1-2FFFC0780CD4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1282,11 +1564,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>202</v>
+      <c r="B2" t="s" s="0">
+        <v>314</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1326,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1896A5-4A20-464B-B3EE-DD3C4B0C920F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1374,11 +1656,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>205</v>
+      <c r="B2" t="s" s="0">
+        <v>317</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1418,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54E326C7-21E5-40F4-8756-B1DCDDF59712}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1466,11 +1748,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>203</v>
+      <c r="B2" t="s" s="0">
+        <v>315</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1510,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A5DADB-B875-4ED0-BAAB-C626A1275FBA}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1558,11 +1840,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>206</v>
+      <c r="B2" t="s" s="0">
+        <v>318</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1602,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC015241-DD51-413A-ABA2-531B88CFD6BF}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1650,11 +1932,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>204</v>
+      <c r="B2" t="s" s="0">
+        <v>316</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1694,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AD9007-FD94-4E29-BB51-10CABB4EC397}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1742,11 +2024,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>242</v>
+      <c r="B2" t="s" s="0">
+        <v>294</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1786,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F04687-B59B-46D6-8BF8-0A93AB876094}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1834,11 +2116,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>228</v>
+      <c r="A2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>308</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1880,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA996DC7-2B69-49B3-8FEC-DFD28BA375B4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1928,11 +2210,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>229</v>
+      <c r="B2" t="s" s="0">
+        <v>309</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1974,7 +2256,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA68FB5D-A8D4-4344-8AF2-635EF93F16A9}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2022,11 +2304,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>195</v>
+      <c r="B2" t="s" s="0">
+        <v>307</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2068,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAE97E4-0C89-4262-92EF-7E437483CC8F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2116,11 +2398,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>221</v>
+      <c r="B2" t="s" s="0">
+        <v>332</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2162,7 +2444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1039392-6523-4FDE-801A-D0A7D43A0B54}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2210,11 +2492,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>218</v>
+      <c r="B2" t="s" s="0">
+        <v>329</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2256,7 +2538,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E276A7-EB97-456B-812D-9154925256E7}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2304,11 +2586,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>222</v>
+      <c r="B2" t="s" s="0">
+        <v>333</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2350,7 +2632,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5859CD-196C-4315-B7CB-91A002AA2A54}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2398,11 +2680,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>223</v>
+      <c r="B2" t="s" s="0">
+        <v>334</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2444,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3412B253-BE44-4456-AB35-9DEB069167CD}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2492,11 +2774,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>227</v>
+      <c r="A2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>302</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2538,7 +2820,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC53AAB-4A4F-43EE-A025-946A96E2F082}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2586,11 +2868,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>191</v>
+      <c r="B2" t="s" s="0">
+        <v>303</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2632,7 +2914,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E23BBE6-AFF2-4C7E-AD13-107791BC34BB}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2680,11 +2962,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>226</v>
+      <c r="B2" t="s" s="0">
+        <v>301</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2726,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6446D34-C859-46B2-8F87-4751ECFB4996}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2774,11 +3056,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>239</v>
+      <c r="B2" t="s" s="0">
+        <v>323</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2820,7 +3102,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD22891C-B5F1-406E-BC4F-B40ADE600751}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2868,11 +3150,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>240</v>
+      <c r="B2" t="s" s="0">
+        <v>325</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2914,7 +3196,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C54289-67FE-4A83-84EB-BB68F2928DAE}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2962,11 +3244,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>213</v>
+      <c r="B2" t="s" s="0">
+        <v>324</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3008,7 +3290,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C14AFC2-69D3-40DF-81D9-0461DF720F8B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3059,11 +3341,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>185</v>
+      <c r="B2" t="s" s="0">
+        <v>297</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3107,7 +3389,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38A8B74-B167-4D84-9AE3-171C2999412B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3158,11 +3440,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>224</v>
+      <c r="B2" t="s" s="0">
+        <v>296</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3206,7 +3488,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2677F800-9CCC-41CB-A720-49DEF58138F4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3254,11 +3536,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>219</v>
+      <c r="B2" t="s" s="0">
+        <v>330</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3300,7 +3582,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953267AE-5EF5-4310-9CB1-35C5C9EC841E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3351,10 +3633,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
       <c r="C2" s="2"/>
@@ -3399,7 +3681,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD030EC-B3B5-485C-95D6-C24F69A18BFD}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3450,10 +3732,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
       <c r="C2" s="2"/>
@@ -3498,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3981E407-FC13-40B3-87B9-13C6511EA533}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3549,10 +3831,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
       <c r="C2" s="2"/>
@@ -3597,7 +3879,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13779E3A-8795-4E07-A53B-2667F40543C6}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -3648,10 +3930,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>42</v>
       </c>
       <c r="C2" s="2"/>
@@ -3696,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33510FF-D609-4CBB-88F3-62D4AD35558D}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3744,11 +4026,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>183</v>
+      <c r="A2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>336</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3792,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6DE354-B30D-4190-ABD0-912AF21F80F6}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3840,11 +4122,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>215</v>
+      <c r="B2" t="s" s="0">
+        <v>326</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3888,7 +4170,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F123EA8D-475C-4BD5-9557-04D3476610AB}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3936,11 +4218,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>216</v>
+      <c r="B2" t="s" s="0">
+        <v>327</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3984,7 +4266,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93EC503-2C46-4C23-98EB-D7EBFCA15861}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4032,11 +4314,11 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>241</v>
+      <c r="B2" t="s" s="0">
+        <v>328</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4080,7 +4362,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61F093D4-B76D-4771-930F-BFC16D8F23A2}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4128,10 +4410,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>41</v>
       </c>
       <c r="C2" s="2"/>
@@ -4176,7 +4458,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2F5EF4-293E-4FBA-854F-4D8FBFA201D5}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4224,11 +4506,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>187</v>
+      <c r="B2" t="s" s="0">
+        <v>299</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4268,7 +4550,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E5D659-04C1-4FED-B9FE-431A2FBE5022}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4316,11 +4598,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>201</v>
+      <c r="B2" t="s" s="0">
+        <v>313</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4362,7 +4644,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05125C6E-9620-4C6C-98C6-4EC52AF18389}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4410,11 +4692,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>232</v>
+      <c r="B2" t="s" s="0">
+        <v>320</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4454,7 +4736,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B63368-81F7-4368-9ECD-48DA475CCB2B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4502,11 +4784,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>234</v>
+      <c r="B2" t="s" s="0">
+        <v>322</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4546,7 +4828,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43865026-B2AE-4F6C-99A7-299098DBB51B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4594,11 +4876,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>236</v>
+      <c r="B2" t="s" s="0">
+        <v>293</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4638,7 +4920,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B442581-EDAC-4FC4-A94E-0ECDB4E2B720}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4686,11 +4968,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>238</v>
+      <c r="B2" t="s" s="0">
+        <v>292</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4730,7 +5012,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C34E9A6-18FA-47DA-8CAD-7C400147C1DF}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4778,11 +5060,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>225</v>
+      <c r="B2" t="s" s="0">
+        <v>298</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4822,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E53910B-13D5-4FFA-B56A-38F248478C99}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4870,11 +5152,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>231</v>
+      <c r="B2" t="s" s="0">
+        <v>319</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4914,7 +5196,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01EA9C5-EF49-4C94-8479-814858E67770}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4962,11 +5244,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>209</v>
+      <c r="B2" t="s" s="0">
+        <v>321</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5006,7 +5288,7 @@
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864E5958-406B-4FDC-8B9E-50EFB9DE74B7}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5054,11 +5336,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>235</v>
+      <c r="B2" t="s" s="0">
+        <v>272</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5098,7 +5380,7 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9804B3CE-92C3-4EFC-95CC-62825FAB22B0}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5146,11 +5428,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>237</v>
+      <c r="B2" t="s" s="0">
+        <v>273</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5190,7 +5472,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1B9718-D45F-4DCA-9C3D-3DEA47AFA8B0}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5238,11 +5520,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>188</v>
+      <c r="B2" t="s" s="0">
+        <v>300</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5282,7 +5564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0781833-229F-4D62-901A-C0E2A289AD08}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5330,10 +5612,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>45</v>
       </c>
       <c r="C2" s="2"/>
@@ -5376,7 +5658,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D52D84A4-D9A0-4774-ACEC-134EDA39FD0E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5424,11 +5706,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>220</v>
+      <c r="B2" t="s" s="0">
+        <v>331</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5470,7 +5752,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5518,11 +5800,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>193</v>
+      <c r="B2" t="s" s="0">
+        <v>305</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5567,7 +5849,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E16C344-7C89-4CA7-A895-528DB802957C}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5615,11 +5897,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>194</v>
+      <c r="A2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>306</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5661,7 +5943,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1442301-F429-411B-933D-81F4E3BB01D8}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5709,11 +5991,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>192</v>
+      <c r="B2" t="s" s="0">
+        <v>304</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2236" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="474">
   <si>
     <t>Result</t>
   </si>
@@ -1084,6 +1084,417 @@
   </si>
   <si>
     <t>Wed Aug 26 21:10:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 23:37:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 02 23:45:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 02:14:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:17:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:19:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:22:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:26:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:28:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:30:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:34:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:35:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:36:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:40:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:41:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:43:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:44:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:45:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:51:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:53:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:54:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 07:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:00:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:02:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:03:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:07:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:13:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:21:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:30:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:30:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:33:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:36:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:53:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:55:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:57:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:58:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 08:59:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:24:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:27:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:44:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:48:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 21:57:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 22:04:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 22:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 05 22:12:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 08:10:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 15:51:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 15:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 15:56:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:01:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:04:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:07:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:15:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:16:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:18:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:21:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:26:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:27:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:29:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:34:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:35:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:38:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:39:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:44:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:46:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:47:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:50:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:51:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 16:57:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:20:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:31:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:35:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 17:58:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:11:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:13:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:14:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:26:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:30:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:36:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:46:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:56:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:57:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 21 18:58:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:47:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:49:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:54:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:57:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 00:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:05:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:07:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:10:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:12:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:12:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:15:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:16:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:24:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:26:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:27:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:29:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:34:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:35:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:40:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:41:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:47:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:50:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:56:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 01:58:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:02:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:27:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:28:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:29:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:30:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:35:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:40:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 02:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 03:02:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 03:03:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 03:04:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1885,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>311</v>
+        <v>449</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1565,10 +1976,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>314</v>
+        <v>452</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1657,10 +2068,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>317</v>
+        <v>455</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1752,7 +2163,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>315</v>
+        <v>453</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1841,10 +2252,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>318</v>
+        <v>456</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1933,10 +2344,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>316</v>
+        <v>454</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2028,7 +2439,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>294</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2117,10 +2528,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>308</v>
+        <v>446</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2214,7 +2625,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>309</v>
+        <v>447</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2305,10 +2716,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>307</v>
+        <v>445</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2402,7 +2813,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>332</v>
+        <v>471</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2493,10 +2904,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>329</v>
+        <v>468</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2590,7 +3001,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>333</v>
+        <v>472</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2684,7 +3095,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>334</v>
+        <v>473</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2775,10 +3186,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>302</v>
+        <v>440</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2872,7 +3283,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>303</v>
+        <v>441</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2963,10 +3374,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>301</v>
+        <v>439</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3057,10 +3468,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>323</v>
+        <v>462</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3154,7 +3565,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>325</v>
+        <v>464</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3248,7 +3659,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>324</v>
+        <v>463</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3345,7 +3756,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>297</v>
+        <v>435</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3444,7 +3855,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>296</v>
+        <v>434</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3540,7 +3951,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4027,10 +4438,10 @@
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>336</v>
+        <v>433</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4126,7 +4537,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>326</v>
+        <v>465</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4222,7 +4633,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>327</v>
+        <v>466</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4318,7 +4729,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>328</v>
+        <v>467</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4510,7 +4921,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>299</v>
+        <v>437</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4599,10 +5010,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>313</v>
+        <v>451</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4696,7 +5107,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>320</v>
+        <v>458</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4788,7 +5199,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>322</v>
+        <v>460</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4877,10 +5288,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>293</v>
+        <v>368</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4972,7 +5383,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5064,7 +5475,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>298</v>
+        <v>436</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5156,7 +5567,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>319</v>
+        <v>457</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5248,7 +5659,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>321</v>
+        <v>459</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5337,10 +5748,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>272</v>
+        <v>461</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5429,10 +5840,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>273</v>
+        <v>420</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5524,7 +5935,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>300</v>
+        <v>438</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5710,7 +6121,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>331</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5804,7 +6215,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>305</v>
+        <v>443</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5901,7 +6312,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>306</v>
+        <v>444</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5995,7 +6406,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>304</v>
+        <v>442</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsACH_27.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="514">
   <si>
     <t>Result</t>
   </si>
@@ -1495,6 +1495,126 @@
   </si>
   <si>
     <t>Fri Oct 23 03:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:43:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 00:55:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:00:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:01:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:02:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:05:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:08:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:11:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:21:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:22:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:29:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:32:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:34:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:42:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:49:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 01:52:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:09:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:10:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:16:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:21:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:31:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:40:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:42:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Oct 24 02:43:17 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +2005,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1976,10 +2096,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2068,10 +2188,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2163,7 +2283,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2252,10 +2372,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2344,10 +2464,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2531,7 +2651,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2625,7 +2745,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2719,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2813,7 +2933,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>471</v>
+        <v>511</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2904,10 +3024,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>468</v>
+        <v>508</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3001,7 +3121,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3095,7 +3215,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>473</v>
+        <v>513</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3189,7 +3309,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3283,7 +3403,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3377,7 +3497,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3468,10 +3588,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3565,7 +3685,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3659,7 +3779,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>463</v>
+        <v>503</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3756,7 +3876,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3855,7 +3975,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3951,7 +4071,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4441,7 +4561,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4537,7 +4657,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>465</v>
+        <v>505</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4633,7 +4753,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>466</v>
+        <v>506</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4729,7 +4849,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>467</v>
+        <v>507</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4921,7 +5041,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5010,10 +5130,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5107,7 +5227,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5199,7 +5319,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5475,7 +5595,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5567,7 +5687,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5656,10 +5776,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -5935,7 +6055,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -6121,7 +6241,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -6215,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -6309,10 +6429,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -6406,7 +6526,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
